--- a/table/resources/sample/DailyRecharge.xlsx
+++ b/table/resources/sample/DailyRecharge.xlsx
@@ -78,12 +78,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1_1|2_2 ： 渠道1id_对应的商品id|渠道2id_对应的商品id
+注：1 =  google渠道ID；2 = apple 渠道ID
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
   <si>
     <t>序列ID</t>
   </si>
@@ -106,10 +130,19 @@
     <t>购买费用</t>
   </si>
   <si>
+    <t>渠道商品ID</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
-    <t>map&lt;int{_}int&gt;{;}</t>
+    <t>map&lt;int{_}long&gt;{;}</t>
+  </si>
+  <si>
+    <t>BigDecimal</t>
+  </si>
+  <si>
+    <t>map&lt;int{_}String&gt;{|}</t>
   </si>
   <si>
     <t>id</t>
@@ -133,16 +166,31 @@
     <t>cost</t>
   </si>
   <si>
+    <t>channelCommodity</t>
+  </si>
+  <si>
     <t>1990000_1000000;1010302_3;1022502_10</t>
   </si>
   <si>
+    <t>1_google199|2_ios199</t>
+  </si>
+  <si>
     <t>1990000_2000000;1023003_10;1023004_15</t>
   </si>
   <si>
+    <t>1_google399|2_ios399</t>
+  </si>
+  <si>
     <t>1990000_3000000;1023103_5;1023104_8;1023304_20</t>
   </si>
   <si>
+    <t>1_google799|2_ios799</t>
+  </si>
+  <si>
     <t>1990000_4000000;1023202_8;1023203_10;1023404_15</t>
+  </si>
+  <si>
+    <t>1_google999|2_ios999</t>
   </si>
   <si>
     <t>1990000_1000000</t>
@@ -1356,8 +1404,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="7" customWidth="1"/>
     <col min="3" max="3" width="8.875" customWidth="1"/>
@@ -1365,9 +1413,10 @@
     <col min="5" max="5" width="8.875" customWidth="1"/>
     <col min="6" max="6" width="10.125" customWidth="1"/>
     <col min="7" max="7" width="19.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="16.5" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1389,54 +1438,63 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="16.5" spans="1:7">
+    <row r="2" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>7</v>
-      </c>
       <c r="F2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="16.5" spans="1:7">
+    <row r="3" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="16.5" spans="1:7">
+    <row r="4" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1445,7 +1503,7 @@
       <c r="F4" s="3"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -1456,7 +1514,7 @@
         <v>57013</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E5" s="7">
         <v>999</v>
@@ -1465,10 +1523,13 @@
         <v>1</v>
       </c>
       <c r="G5" s="8">
-        <v>2999</v>
+        <v>1.99</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6" s="7">
         <v>2</v>
       </c>
@@ -1479,7 +1540,7 @@
         <v>57013</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E6" s="7">
         <v>999</v>
@@ -1488,10 +1549,13 @@
         <v>1</v>
       </c>
       <c r="G6" s="8">
-        <v>3999</v>
+        <v>3.99</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="A7" s="7">
         <v>3</v>
       </c>
@@ -1502,7 +1566,7 @@
         <v>57013</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E7" s="7">
         <v>999</v>
@@ -1511,10 +1575,13 @@
         <v>1</v>
       </c>
       <c r="G7" s="8">
-        <v>5999</v>
+        <v>7.99</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="A8" s="7">
         <v>4</v>
       </c>
@@ -1525,7 +1592,7 @@
         <v>57013</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E8" s="7">
         <v>999</v>
@@ -1534,10 +1601,13 @@
         <v>1</v>
       </c>
       <c r="G8" s="8">
-        <v>6999</v>
+        <v>9.99</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>101</v>
       </c>
@@ -1548,7 +1618,7 @@
         <v>57013</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1557,7 +1627,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>102</v>
       </c>
@@ -1568,7 +1638,7 @@
         <v>57013</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1577,7 +1647,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>103</v>
       </c>
@@ -1588,7 +1658,7 @@
         <v>57013</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1597,7 +1667,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>104</v>
       </c>
@@ -1608,7 +1678,7 @@
         <v>57013</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1617,7 +1687,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>105</v>
       </c>
@@ -1628,7 +1698,7 @@
         <v>57013</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E13">
         <v>1</v>

--- a/table/resources/sample/DailyRecharge.xlsx
+++ b/table/resources/sample/DailyRecharge.xlsx
@@ -96,6 +96,29 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+“XX% SALL”标签,可以不配置 不显示
+注：XX = 百分比数值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 1_1|2_2 ： 渠道1id_对应的商品id|渠道2id_对应的商品id
 注：1 =  google渠道ID；2 = apple 渠道ID
 </t>
@@ -107,7 +130,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
   <si>
     <t>序列ID</t>
   </si>
@@ -130,6 +153,9 @@
     <t>购买费用</t>
   </si>
   <si>
+    <t>标签1</t>
+  </si>
+  <si>
     <t>渠道商品ID</t>
   </si>
   <si>
@@ -164,6 +190,9 @@
   </si>
   <si>
     <t>cost</t>
+  </si>
+  <si>
+    <t>label1</t>
   </si>
   <si>
     <t>channelCommodity</t>
@@ -595,12 +624,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -727,7 +771,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -739,34 +783,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -851,7 +895,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -867,11 +911,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -1404,8 +1454,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="7" customWidth="1"/>
     <col min="3" max="3" width="8.875" customWidth="1"/>
@@ -1414,9 +1464,10 @@
     <col min="6" max="6" width="10.125" customWidth="1"/>
     <col min="7" max="7" width="19.5" style="2" customWidth="1"/>
     <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="9" max="9" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="16.5" spans="1:8">
+    <row r="1" s="1" customFormat="1" ht="16.5" spans="1:9">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1438,63 +1489,72 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="16.5" spans="1:8">
+    <row r="2" s="1" customFormat="1" ht="16.5" spans="1:9">
       <c r="A2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>8</v>
+      <c r="D2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>9</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="H2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="16.5" spans="1:8">
+    <row r="3" s="1" customFormat="1" ht="16.5" spans="1:9">
       <c r="A3" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="G3" s="6" t="s">
         <v>19</v>
       </c>
+      <c r="H3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="16.5" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="16.5" spans="1:9">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1502,112 +1562,125 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="7">
+    <row r="5" spans="1:9">
+      <c r="A5" s="9">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="9">
         <v>1</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="9">
         <v>57013</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="7">
+      <c r="D5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="9">
         <v>999</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="9">
         <v>1</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="10">
         <v>1.99</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>21</v>
+      <c r="H5" s="10">
+        <v>200</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="7">
+    <row r="6" spans="1:9">
+      <c r="A6" s="9">
         <v>2</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="9">
         <v>1</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="9">
         <v>57013</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="7">
+      <c r="D6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="9">
         <v>999</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="9">
         <v>1</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="10">
         <v>3.99</v>
       </c>
-      <c r="H6" s="8" t="s">
-        <v>23</v>
+      <c r="H6" s="10">
+        <v>300</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="7">
+    <row r="7" spans="1:9">
+      <c r="A7" s="9">
         <v>3</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="9">
         <v>1</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="9">
         <v>57013</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="7">
+      <c r="D7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="9">
         <v>999</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="9">
         <v>1</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="10">
         <v>7.99</v>
       </c>
-      <c r="H7" s="8" t="s">
-        <v>25</v>
+      <c r="H7" s="10">
+        <v>500</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="7">
+    <row r="8" spans="1:9">
+      <c r="A8" s="9">
         <v>4</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="9">
         <v>1</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="9">
         <v>57013</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="7">
+      <c r="D8" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="9">
         <v>999</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="9">
         <v>1</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="10">
         <v>9.99</v>
       </c>
-      <c r="H8" s="8" t="s">
-        <v>27</v>
+      <c r="H8" s="10">
+        <v>800</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>101</v>
       </c>
@@ -1618,7 +1691,7 @@
         <v>57013</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1627,7 +1700,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>102</v>
       </c>
@@ -1638,7 +1711,7 @@
         <v>57013</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1647,7 +1720,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>103</v>
       </c>
@@ -1658,7 +1731,7 @@
         <v>57013</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1667,7 +1740,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>104</v>
       </c>
@@ -1678,7 +1751,7 @@
         <v>57013</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1687,7 +1760,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>105</v>
       </c>
@@ -1698,7 +1771,7 @@
         <v>57013</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E13">
         <v>1</v>
